--- a/bit/比特配置文件.xlsx
+++ b/bit/比特配置文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26331" windowHeight="12102"/>
+    <workbookView windowHeight="17205"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="96">
   <si>
     <t>窗口ID</t>
   </si>
@@ -42,301 +42,280 @@
     <t>站点</t>
   </si>
   <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>1495e31cb630406bb690ba187f264fe7</t>
+  </si>
+  <si>
+    <t>vngbjkk</t>
+  </si>
+  <si>
+    <t>墨西哥</t>
+  </si>
+  <si>
+    <t>9812f185f7ab49d98f3988994d9e8ebf</t>
+  </si>
+  <si>
+    <t>龙</t>
+  </si>
+  <si>
+    <t>墨西哥，阿根廷</t>
+  </si>
+  <si>
+    <t>6af1cc457342417db4e7235d7a062f2f</t>
+  </si>
+  <si>
+    <t>腾</t>
+  </si>
+  <si>
+    <t>891d56c43ce0449182bef33695a386ff</t>
+  </si>
+  <si>
+    <t>虎</t>
+  </si>
+  <si>
+    <t>忽略</t>
+  </si>
+  <si>
+    <t>墨西哥，巴西，阿根廷</t>
+  </si>
+  <si>
+    <t>23abe995037b4efeba2159a0a17df939</t>
+  </si>
+  <si>
+    <t>德德智汇</t>
+  </si>
+  <si>
+    <t>a5cb29d875e84c8580d3f68a0d658533</t>
+  </si>
+  <si>
+    <t>德德智慧</t>
+  </si>
+  <si>
+    <t>43e74c662e474a6895fe88874ac88821</t>
+  </si>
+  <si>
+    <t>跃</t>
+  </si>
+  <si>
+    <t>22139511815a4bf588fe96d5fdafded6</t>
+  </si>
+  <si>
+    <t>四季如春</t>
+  </si>
+  <si>
+    <t>813cdb4042e34e61a78bf16f756df7fc</t>
+  </si>
+  <si>
+    <t>五福临门</t>
+  </si>
+  <si>
+    <t>7c68f33100064d1f8ee82f79a667b223</t>
+  </si>
+  <si>
+    <t>六六大顺</t>
+  </si>
+  <si>
+    <t>9db3976d84ec44abb07c75af556c5243</t>
+  </si>
+  <si>
+    <t>七星高照</t>
+  </si>
+  <si>
+    <t>5c9af39c13ae47bca3779b2ec55cc481</t>
+  </si>
+  <si>
+    <t>八方来财</t>
+  </si>
+  <si>
+    <t>c5fb7600995c4cbabd6e8e6c30b2661f</t>
+  </si>
+  <si>
+    <t>策马奔腾</t>
+  </si>
+  <si>
+    <t>55d3db6471dc4262aa5dd2de190e2422</t>
+  </si>
+  <si>
+    <t>春暖花开</t>
+  </si>
+  <si>
+    <t>c5aac686addf4038aa02cf2d16d1423f</t>
+  </si>
+  <si>
+    <t>钱途无量</t>
+  </si>
+  <si>
+    <t>d3b94c89e527423aa7f2c5c8dc0a2190</t>
+  </si>
+  <si>
+    <t>鸿运当头</t>
+  </si>
+  <si>
+    <t>b2323ff45855401689ab16ed11d4ed20</t>
+  </si>
+  <si>
+    <t>一跃千里</t>
+  </si>
+  <si>
+    <t>d49c1865ae404364b05391a79fd6bc65</t>
+  </si>
+  <si>
+    <t>风调雨顺</t>
+  </si>
+  <si>
+    <t>187700d9c3424c0eb6d8a75d92bf3b9c</t>
+  </si>
+  <si>
+    <t>跃马扬鞭</t>
+  </si>
+  <si>
+    <t>墨西哥，巴西，智利，阿根廷，乌拉圭</t>
+  </si>
+  <si>
+    <t>3e4c34d0833e4221b262291bddaac899</t>
+  </si>
+  <si>
+    <t>大展宏图</t>
+  </si>
+  <si>
+    <t>764e7e53c57247d7aaa88fb23849f7c9</t>
+  </si>
+  <si>
+    <t>马到成功</t>
+  </si>
+  <si>
+    <t>55655ec7c5db43149f5640810197f35c</t>
+  </si>
+  <si>
+    <t>健步如飞</t>
+  </si>
+  <si>
+    <t>6190adcc6a3543a8b5fdb7189dfc3802</t>
+  </si>
+  <si>
+    <t>健步如飞1</t>
+  </si>
+  <si>
+    <t>227420bac08049c5a508a2f95510bef4</t>
+  </si>
+  <si>
+    <t>健步如飞2</t>
+  </si>
+  <si>
+    <t>ee50561ad3d242fdb82b42864481a11f</t>
+  </si>
+  <si>
+    <t>健步如飞3</t>
+  </si>
+  <si>
+    <t>3f97a677aba2418081db3f9ca8120fb6</t>
+  </si>
+  <si>
+    <t>飞黄腾达2</t>
+  </si>
+  <si>
+    <t>8282ffc163ee46c783cc5b4db71f7479</t>
+  </si>
+  <si>
+    <t>飞黄腾达3</t>
+  </si>
+  <si>
+    <t>33387c91f36241359c0eb0d17be8f974</t>
+  </si>
+  <si>
+    <t>飞黄腾达5</t>
+  </si>
+  <si>
+    <t>0480d1e8bd84425b9288a8de5fefa1d8</t>
+  </si>
+  <si>
+    <t>招财猫</t>
+  </si>
+  <si>
+    <t>2545d72510084276a752568608eaaf76</t>
+  </si>
+  <si>
+    <t>旺财狗</t>
+  </si>
+  <si>
+    <t>1449270209804ffda0a7d4e83d22b940</t>
+  </si>
+  <si>
+    <t>杨柳依依1</t>
+  </si>
+  <si>
+    <t>2aae34e81b9e40e9860b6658fb7894cc</t>
+  </si>
+  <si>
+    <t>杨柳依依2</t>
+  </si>
+  <si>
+    <t>3395db0467064b91988ad8c9b9877412</t>
+  </si>
+  <si>
+    <t>杨柳依依3</t>
+  </si>
+  <si>
+    <t>40bcae59448d4745a8622993f1a07cd3</t>
+  </si>
+  <si>
+    <t>杨柳依依4</t>
+  </si>
+  <si>
+    <t>315b0b0575884e7181cefaa8a6301f96</t>
+  </si>
+  <si>
+    <t>钱程似锦</t>
+  </si>
+  <si>
+    <t>4d91befc3d5746518e33d50487e00033</t>
+  </si>
+  <si>
+    <t>钱程似锦2</t>
+  </si>
+  <si>
+    <t>987270a6587b46eeaeac11e9b928e88d</t>
+  </si>
+  <si>
+    <t>钱程似锦3</t>
+  </si>
+  <si>
+    <t>b1127c7a20bd4952bbc06c41e1b226c5</t>
+  </si>
+  <si>
+    <t>前程似锦4</t>
+  </si>
+  <si>
+    <t>00287da1c0964c6889a239c98547b0f5</t>
+  </si>
+  <si>
+    <t>钱程似锦5</t>
+  </si>
+  <si>
+    <t>df2d33b20d0b4d72949fc490f7ff075a</t>
+  </si>
+  <si>
+    <t>龙争虎斗</t>
+  </si>
+  <si>
+    <t>b2f7baeb363346af8d81dd20dd945ef4</t>
+  </si>
+  <si>
+    <t>龙马精神</t>
+  </si>
+  <si>
     <t>1f22b75033a84d64bff59c3a41ea6047</t>
   </si>
   <si>
     <t>龙吟虎啸</t>
   </si>
   <si>
-    <t>墨西哥，巴西，阿根廷</t>
-  </si>
-  <si>
-    <t>b2f7baeb363346af8d81dd20dd945ef4</t>
-  </si>
-  <si>
-    <t>龙马精神</t>
-  </si>
-  <si>
-    <t>df2d33b20d0b4d72949fc490f7ff075a</t>
-  </si>
-  <si>
-    <t>龙争虎斗</t>
-  </si>
-  <si>
     <t>38fcac77fbf641ed8b6cbc1c2aedc5b2</t>
   </si>
   <si>
     <t>龙凤呈祥</t>
-  </si>
-  <si>
-    <t>04f8351f2dd04afcad3a488dc53a4482</t>
-  </si>
-  <si>
-    <t>钱军5</t>
-  </si>
-  <si>
-    <t>忽略</t>
-  </si>
-  <si>
-    <t>b1127c7a20bd4952bbc06c41e1b226c5</t>
-  </si>
-  <si>
-    <t>钱军4</t>
-  </si>
-  <si>
-    <t>a6de8a3a7776481faedf942cd1928a3d</t>
-  </si>
-  <si>
-    <t>发财猪</t>
-  </si>
-  <si>
-    <t>e042c21cd01c4dfbbdff56c887e44c67</t>
-  </si>
-  <si>
-    <t>赵红</t>
-  </si>
-  <si>
-    <t>00287da1c0964c6889a239c98547b0f5</t>
-  </si>
-  <si>
-    <t>钱曼</t>
-  </si>
-  <si>
-    <t>ed544925816a4ec7a7caf47a3ec3ee34</t>
-  </si>
-  <si>
-    <t>雷肖4</t>
-  </si>
-  <si>
-    <t>987270a6587b46eeaeac11e9b928e88d</t>
-  </si>
-  <si>
-    <t>钱军3</t>
-  </si>
-  <si>
-    <t>4d91befc3d5746518e33d50487e00033</t>
-  </si>
-  <si>
-    <t>钱军2</t>
-  </si>
-  <si>
-    <t>315b0b0575884e7181cefaa8a6301f96</t>
-  </si>
-  <si>
-    <t>钱军1</t>
-  </si>
-  <si>
-    <t>40bcae59448d4745a8622993f1a07cd3</t>
-  </si>
-  <si>
-    <t>杨家华4</t>
-  </si>
-  <si>
-    <t>3395db0467064b91988ad8c9b9877412</t>
-  </si>
-  <si>
-    <t>杨家华3</t>
-  </si>
-  <si>
-    <t>2aae34e81b9e40e9860b6658fb7894cc</t>
-  </si>
-  <si>
-    <t>杨家华2</t>
-  </si>
-  <si>
-    <t>1449270209804ffda0a7d4e83d22b940</t>
-  </si>
-  <si>
-    <t>杨家华1</t>
-  </si>
-  <si>
-    <t>2545d72510084276a752568608eaaf76</t>
-  </si>
-  <si>
-    <t>旺财狗</t>
-  </si>
-  <si>
-    <t>0480d1e8bd84425b9288a8de5fefa1d8</t>
-  </si>
-  <si>
-    <t>招财猫</t>
-  </si>
-  <si>
-    <t>33387c91f36241359c0eb0d17be8f974</t>
-  </si>
-  <si>
-    <t>飞黄腾达5</t>
-  </si>
-  <si>
-    <t>8282ffc163ee46c783cc5b4db71f7479</t>
-  </si>
-  <si>
-    <t>飞黄腾达3</t>
-  </si>
-  <si>
-    <t>3f97a677aba2418081db3f9ca8120fb6</t>
-  </si>
-  <si>
-    <t>飞黄腾达2</t>
-  </si>
-  <si>
-    <t>ee50561ad3d242fdb82b42864481a11f</t>
-  </si>
-  <si>
-    <t>健步如飞3</t>
-  </si>
-  <si>
-    <t>227420bac08049c5a508a2f95510bef4</t>
-  </si>
-  <si>
-    <t>健步如飞2</t>
-  </si>
-  <si>
-    <t>6190adcc6a3543a8b5fdb7189dfc3802</t>
-  </si>
-  <si>
-    <t>健步如飞1</t>
-  </si>
-  <si>
-    <t>55655ec7c5db43149f5640810197f35c</t>
-  </si>
-  <si>
-    <t>健步如飞</t>
-  </si>
-  <si>
-    <t>764e7e53c57247d7aaa88fb23849f7c9</t>
-  </si>
-  <si>
-    <t>马到成功</t>
-  </si>
-  <si>
-    <t>3e4c34d0833e4221b262291bddaac899</t>
-  </si>
-  <si>
-    <t>大展宏图</t>
-  </si>
-  <si>
-    <t>187700d9c3424c0eb6d8a75d92bf3b9c</t>
-  </si>
-  <si>
-    <t>跃马扬鞭</t>
-  </si>
-  <si>
-    <t>墨西哥，巴西，智利，阿根廷，乌拉圭</t>
-  </si>
-  <si>
-    <t>d49c1865ae404364b05391a79fd6bc65</t>
-  </si>
-  <si>
-    <t>风调雨顺</t>
-  </si>
-  <si>
-    <t>b2323ff45855401689ab16ed11d4ed20</t>
-  </si>
-  <si>
-    <t>一跃千里</t>
-  </si>
-  <si>
-    <t>d3b94c89e527423aa7f2c5c8dc0a2190</t>
-  </si>
-  <si>
-    <t>鸿运当头</t>
-  </si>
-  <si>
-    <t>c5aac686addf4038aa02cf2d16d1423f</t>
-  </si>
-  <si>
-    <t>钱途无量</t>
-  </si>
-  <si>
-    <t>55d3db6471dc4262aa5dd2de190e2422</t>
-  </si>
-  <si>
-    <t>春暖花开</t>
-  </si>
-  <si>
-    <t>c5fb7600995c4cbabd6e8e6c30b2661f</t>
-  </si>
-  <si>
-    <t>策马奔腾</t>
-  </si>
-  <si>
-    <t>5c9af39c13ae47bca3779b2ec55cc481</t>
-  </si>
-  <si>
-    <t>八方来财</t>
-  </si>
-  <si>
-    <t>9db3976d84ec44abb07c75af556c5243</t>
-  </si>
-  <si>
-    <t>七星高照</t>
-  </si>
-  <si>
-    <t>7c68f33100064d1f8ee82f79a667b223</t>
-  </si>
-  <si>
-    <t>六六大顺</t>
-  </si>
-  <si>
-    <t>813cdb4042e34e61a78bf16f756df7fc</t>
-  </si>
-  <si>
-    <t>五福临门</t>
-  </si>
-  <si>
-    <t>22139511815a4bf588fe96d5fdafded6</t>
-  </si>
-  <si>
-    <t>四季如春</t>
-  </si>
-  <si>
-    <t>43e74c662e474a6895fe88874ac88821</t>
-  </si>
-  <si>
-    <t>跃</t>
-  </si>
-  <si>
-    <t>a5cb29d875e84c8580d3f68a0d658533</t>
-  </si>
-  <si>
-    <t>德德智慧</t>
-  </si>
-  <si>
-    <t>23abe995037b4efeba2159a0a17df939</t>
-  </si>
-  <si>
-    <t>德德智汇</t>
-  </si>
-  <si>
-    <t>891d56c43ce0449182bef33695a386ff</t>
-  </si>
-  <si>
-    <t>虎</t>
-  </si>
-  <si>
-    <t>6af1cc457342417db4e7235d7a062f2f</t>
-  </si>
-  <si>
-    <t>腾</t>
-  </si>
-  <si>
-    <t>9812f185f7ab49d98f3988994d9e8ebf</t>
-  </si>
-  <si>
-    <t>龙</t>
-  </si>
-  <si>
-    <t>墨西哥，阿根廷</t>
-  </si>
-  <si>
-    <t>1495e31cb630406bb690ba187f264fe7</t>
-  </si>
-  <si>
-    <t>vngbjkk</t>
-  </si>
-  <si>
-    <t>墨西哥</t>
   </si>
 </sst>
 </file>
@@ -971,17 +950,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1295,601 +1280,695 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="3"/>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="54.4414414414414" customWidth="1"/>
-    <col min="2" max="2" width="15.6216216216216" customWidth="1"/>
-    <col min="3" max="3" width="25.7477477477477" customWidth="1"/>
-    <col min="4" max="4" width="31.036036036036" customWidth="1"/>
+    <col min="1" max="1" width="54.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="25.75" customWidth="1"/>
+    <col min="4" max="4" width="31.0333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="14.25" customHeight="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" ht="28.5" customHeight="1" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="28.5" customHeight="1" spans="1:5">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
       <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22">
         <v>25</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" t="s">
         <v>15</v>
       </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
         <v>15</v>
       </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" t="s">
         <v>15</v>
       </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" t="s">
         <v>15</v>
       </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38">
         <v>41</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="s">
         <v>15</v>
       </c>
-      <c r="D19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39">
         <v>42</v>
       </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E40">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E41">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E42">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" spans="1:5">
+      <c r="A44" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="B44" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E44">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>95</v>
-      </c>
-      <c r="B46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>97</v>
-      </c>
-      <c r="B47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>100</v>
-      </c>
-      <c r="B48" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" t="s">
-        <v>102</v>
+        <v>16</v>
+      </c>
+      <c r="E45">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:E44">
+    <sortCondition ref="E2"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1900,50 +1979,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.61666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" ht="15" spans="1:4">
+    <row r="1" ht="14.25" spans="1:4">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="15" spans="1:4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:4">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/bit/比特配置文件.xlsx
+++ b/bit/比特配置文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21480" windowHeight="12255"/>
+    <workbookView windowHeight="17205"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1886,9 +1886,7 @@
       <c r="B33" t="s">
         <v>71</v>
       </c>
-      <c r="C33" t="s">
-        <v>15</v>
-      </c>
+      <c r="C33"/>
       <c r="D33" t="s">
         <v>16</v>
       </c>
@@ -1903,9 +1901,7 @@
       <c r="B34" t="s">
         <v>73</v>
       </c>
-      <c r="C34" t="s">
-        <v>15</v>
-      </c>
+      <c r="C34"/>
       <c r="D34" t="s">
         <v>16</v>
       </c>
@@ -1920,9 +1916,7 @@
       <c r="B35" t="s">
         <v>75</v>
       </c>
-      <c r="C35" t="s">
-        <v>15</v>
-      </c>
+      <c r="C35"/>
       <c r="D35" t="s">
         <v>16</v>
       </c>
@@ -1971,9 +1965,7 @@
       <c r="B38" t="s">
         <v>81</v>
       </c>
-      <c r="C38" t="s">
-        <v>15</v>
-      </c>
+      <c r="C38"/>
       <c r="D38" t="s">
         <v>16</v>
       </c>
@@ -2005,9 +1997,7 @@
       <c r="B40" t="s">
         <v>85</v>
       </c>
-      <c r="C40" t="s">
-        <v>15</v>
-      </c>
+      <c r="C40"/>
       <c r="D40" t="s">
         <v>16</v>
       </c>
@@ -2022,9 +2012,7 @@
       <c r="B41" t="s">
         <v>87</v>
       </c>
-      <c r="C41" t="s">
-        <v>15</v>
-      </c>
+      <c r="C41"/>
       <c r="D41" t="s">
         <v>16</v>
       </c>
@@ -2180,6 +2168,9 @@
       <c r="B51" t="s">
         <v>106</v>
       </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
       <c r="D51" t="s">
         <v>16</v>
       </c>
@@ -2337,6 +2328,9 @@
       <c r="B62" t="s">
         <v>129</v>
       </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
       <c r="D62" t="s">
         <v>16</v>
       </c>
@@ -2351,6 +2345,9 @@
       <c r="B63" t="s">
         <v>131</v>
       </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
       <c r="D63" t="s">
         <v>16</v>
       </c>
@@ -2365,6 +2362,9 @@
       <c r="B64" t="s">
         <v>133</v>
       </c>
+      <c r="C64" t="s">
+        <v>15</v>
+      </c>
       <c r="D64" t="s">
         <v>16</v>
       </c>
@@ -2379,6 +2379,9 @@
       <c r="B65" t="s">
         <v>135</v>
       </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
       <c r="D65" t="s">
         <v>16</v>
       </c>
@@ -2392,6 +2395,9 @@
       </c>
       <c r="B66" t="s">
         <v>137</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
       </c>
       <c r="D66" t="s">
         <v>16</v>

--- a/bit/比特配置文件.xlsx
+++ b/bit/比特配置文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17205"/>
+    <workbookView windowWidth="24945" windowHeight="17205"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="138">
   <si>
     <t>窗口ID</t>
   </si>
@@ -1600,6 +1600,9 @@
       <c r="B13" t="s">
         <v>32</v>
       </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
@@ -1886,7 +1889,6 @@
       <c r="B33" t="s">
         <v>71</v>
       </c>
-      <c r="C33"/>
       <c r="D33" t="s">
         <v>16</v>
       </c>
@@ -1901,7 +1903,6 @@
       <c r="B34" t="s">
         <v>73</v>
       </c>
-      <c r="C34"/>
       <c r="D34" t="s">
         <v>16</v>
       </c>
@@ -1916,7 +1917,6 @@
       <c r="B35" t="s">
         <v>75</v>
       </c>
-      <c r="C35"/>
       <c r="D35" t="s">
         <v>16</v>
       </c>
@@ -1965,7 +1965,6 @@
       <c r="B38" t="s">
         <v>81</v>
       </c>
-      <c r="C38"/>
       <c r="D38" t="s">
         <v>16</v>
       </c>
@@ -1997,7 +1996,6 @@
       <c r="B40" t="s">
         <v>85</v>
       </c>
-      <c r="C40"/>
       <c r="D40" t="s">
         <v>16</v>
       </c>
@@ -2012,7 +2010,6 @@
       <c r="B41" t="s">
         <v>87</v>
       </c>
-      <c r="C41"/>
       <c r="D41" t="s">
         <v>16</v>
       </c>

--- a/bit/比特配置文件.xlsx
+++ b/bit/比特配置文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24945" windowHeight="17205"/>
+    <workbookView windowWidth="24000" windowHeight="13455"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="186">
   <si>
     <t>窗口ID</t>
   </si>
@@ -141,6 +141,9 @@
     <t>春暖花开</t>
   </si>
   <si>
+    <t>巴西，阿根廷</t>
+  </si>
+  <si>
     <t>c5aac686addf4038aa02cf2d16d1423f</t>
   </si>
   <si>
@@ -363,6 +366,9 @@
     <t>梁山好汉111</t>
   </si>
   <si>
+    <t>墨西哥，巴西</t>
+  </si>
+  <si>
     <t>dae8490852304cf3a08d8a68a137dae1</t>
   </si>
   <si>
@@ -399,6 +405,9 @@
     <t>宁静致远</t>
   </si>
   <si>
+    <t>阿根廷</t>
+  </si>
+  <si>
     <t>70f84da502fc410482be7d9c994988a0</t>
   </si>
   <si>
@@ -442,6 +451,141 @@
   </si>
   <si>
     <t>宁静致远2</t>
+  </si>
+  <si>
+    <t>a1b601a3e3fe4cd893c69007a89feaea</t>
+  </si>
+  <si>
+    <t>宁静致远3</t>
+  </si>
+  <si>
+    <t>30d028302eb644d6b240003e5b923ba6</t>
+  </si>
+  <si>
+    <t>一路长红2</t>
+  </si>
+  <si>
+    <t>b7975c8b198a4b9ca31f5818eebd68cc</t>
+  </si>
+  <si>
+    <t>宁静致远5</t>
+  </si>
+  <si>
+    <t>4c9b4b172c7d404ca71c173c21b6cc4c</t>
+  </si>
+  <si>
+    <t>宁静致远6</t>
+  </si>
+  <si>
+    <t>c6a2806abc7340b9998044019ded84b2</t>
+  </si>
+  <si>
+    <t>德德智汇2</t>
+  </si>
+  <si>
+    <t>6d1ca661527348ba893c6b762043d78d</t>
+  </si>
+  <si>
+    <t>德德智汇3</t>
+  </si>
+  <si>
+    <t>72d8e7188b09459eab3220571b9e6577</t>
+  </si>
+  <si>
+    <t>德德智汇4</t>
+  </si>
+  <si>
+    <t>e08adfb6f7384f63846bab2d98c7d022</t>
+  </si>
+  <si>
+    <t>张健1</t>
+  </si>
+  <si>
+    <t>8e3a288675494673b1f60c7bebaa0948</t>
+  </si>
+  <si>
+    <t>张健2</t>
+  </si>
+  <si>
+    <t>0e49e9e24c3445c4b2819c44958b7066</t>
+  </si>
+  <si>
+    <t>张健3</t>
+  </si>
+  <si>
+    <t>fba66b9f4e9444648f8d8c2c0bc6a2ab</t>
+  </si>
+  <si>
+    <t>张健5</t>
+  </si>
+  <si>
+    <t>3387784b60af4856b32ae823c89ce015</t>
+  </si>
+  <si>
+    <t>张健6</t>
+  </si>
+  <si>
+    <t>b15c1542fb154a68b6ffbee7b868c33d</t>
+  </si>
+  <si>
+    <t>健步如飞（fti）</t>
+  </si>
+  <si>
+    <t>ab4d7d7e9b78450181f485d2253f6d37</t>
+  </si>
+  <si>
+    <t>高风亮节</t>
+  </si>
+  <si>
+    <t>19ba260e1440411196fdedfd4242fb51</t>
+  </si>
+  <si>
+    <t>步步高升</t>
+  </si>
+  <si>
+    <t>7ef3242c7e4940f1bdde99ded71fd825</t>
+  </si>
+  <si>
+    <t>高人一等</t>
+  </si>
+  <si>
+    <t>5b090a4484324c86a4d747574ddd0456</t>
+  </si>
+  <si>
+    <t>金光闪闪</t>
+  </si>
+  <si>
+    <t>4e712461dab04cdaa46f5400a4e8d3c6</t>
+  </si>
+  <si>
+    <t>功成名就</t>
+  </si>
+  <si>
+    <t>76e9492d6e5d4d3c9a564ed5efeb7b74</t>
+  </si>
+  <si>
+    <t>顺财羊</t>
+  </si>
+  <si>
+    <t>杨雨萌2</t>
+  </si>
+  <si>
+    <t>b4a18a93a06f41a58fee027c3a9921c3</t>
+  </si>
+  <si>
+    <t>来财马</t>
+  </si>
+  <si>
+    <t>b2e795192e7144678fc01f9b50e383f1</t>
+  </si>
+  <si>
+    <t>聚财鼠</t>
+  </si>
+  <si>
+    <t>cdc4b2cf5d5843eea6b138f2a1c438c1</t>
+  </si>
+  <si>
+    <t>杨雨萌5</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1547,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="54.4416666666667" customWidth="1"/>
@@ -1618,7 +1762,7 @@
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>18</v>
@@ -1632,7 +1776,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E15">
         <v>19</v>
@@ -1640,10 +1784,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
         <v>16</v>
@@ -1668,13 +1812,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>21</v>
@@ -1682,13 +1826,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>22</v>
@@ -1696,13 +1840,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>23</v>
@@ -1710,13 +1854,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E21">
         <v>24</v>
@@ -1724,10 +1868,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
         <v>16</v>
@@ -1738,13 +1882,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>26</v>
@@ -1752,10 +1896,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
         <v>16</v>
@@ -1766,10 +1910,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
         <v>16</v>
@@ -1780,10 +1924,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
@@ -1794,10 +1938,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
@@ -1808,10 +1952,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
         <v>16</v>
@@ -1822,10 +1966,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
@@ -1836,10 +1980,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
         <v>16</v>
@@ -1850,10 +1994,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
@@ -1867,10 +2011,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>15</v>
@@ -1884,10 +2028,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
@@ -1898,10 +2042,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
         <v>16</v>
@@ -1912,10 +2056,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
         <v>16</v>
@@ -1926,14 +2070,12 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" t="s">
-        <v>15</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C36"/>
       <c r="D36" t="s">
         <v>16</v>
       </c>
@@ -1943,10 +2085,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
@@ -1960,10 +2102,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>16</v>
@@ -1974,10 +2116,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -1991,10 +2133,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
         <v>16</v>
@@ -2005,10 +2147,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
         <v>16</v>
@@ -2019,10 +2161,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
         <v>16</v>
@@ -2033,10 +2175,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
         <v>16</v>
@@ -2047,10 +2189,10 @@
     </row>
     <row r="44" ht="14.25" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
         <v>16</v>
@@ -2061,10 +2203,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D45" t="s">
         <v>16</v>
@@ -2075,10 +2217,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -2092,10 +2234,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -2109,10 +2251,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C48" t="s">
         <v>15</v>
@@ -2126,10 +2268,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C49" t="s">
         <v>15</v>
@@ -2143,10 +2285,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
@@ -2160,10 +2302,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -2177,10 +2319,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
         <v>15</v>
@@ -2194,13 +2336,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B53" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E53">
         <v>56</v>
@@ -2208,13 +2350,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B54" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" t="s">
         <v>112</v>
-      </c>
-      <c r="D54" t="s">
-        <v>16</v>
       </c>
       <c r="E54">
         <v>57</v>
@@ -2222,13 +2364,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E55">
         <v>58</v>
@@ -2236,13 +2378,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E56">
         <v>59</v>
@@ -2250,97 +2392,95 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E57">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B58" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E58">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="E59">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D60" t="s">
         <v>16</v>
       </c>
       <c r="E60">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E61">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
-      </c>
-      <c r="C62" t="s">
-        <v>15</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C62"/>
       <c r="D62" t="s">
         <v>16</v>
       </c>
       <c r="E62">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C63" t="s">
         <v>15</v>
@@ -2349,15 +2489,15 @@
         <v>16</v>
       </c>
       <c r="E63">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B64" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C64" t="s">
         <v>15</v>
@@ -2366,15 +2506,15 @@
         <v>16</v>
       </c>
       <c r="E64">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
         <v>15</v>
@@ -2383,15 +2523,15 @@
         <v>16</v>
       </c>
       <c r="E65">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
@@ -2400,7 +2540,368 @@
         <v>16</v>
       </c>
       <c r="E66">
-        <v>69</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>161</v>
+      </c>
+      <c r="B77" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>16</v>
+      </c>
+      <c r="E78">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="1:5">
+      <c r="A79" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79" t="s">
+        <v>130</v>
+      </c>
+      <c r="E79">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" t="s">
+        <v>168</v>
+      </c>
+      <c r="D80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>169</v>
+      </c>
+      <c r="B81" t="s">
+        <v>170</v>
+      </c>
+      <c r="D81" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="D82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" t="s">
+        <v>176</v>
+      </c>
+      <c r="D84" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>177</v>
+      </c>
+      <c r="B85" t="s">
+        <v>178</v>
+      </c>
+      <c r="D85" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>177</v>
+      </c>
+      <c r="B86" t="s">
+        <v>179</v>
+      </c>
+      <c r="D86" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>180</v>
+      </c>
+      <c r="B87" t="s">
+        <v>181</v>
+      </c>
+      <c r="D87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>182</v>
+      </c>
+      <c r="B88" t="s">
+        <v>183</v>
+      </c>
+      <c r="D88" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" spans="1:5">
+      <c r="A89" t="s">
+        <v>184</v>
+      </c>
+      <c r="B89" t="s">
+        <v>185</v>
+      </c>
+      <c r="C89" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2421,10 +2922,10 @@
   <sheetData>
     <row r="1" ht="14.25" spans="1:4">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
         <v>16</v>
@@ -2432,10 +2933,10 @@
     </row>
     <row r="2" ht="14.25" spans="1:4">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -2443,10 +2944,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>

--- a/bit/比特配置文件.xlsx
+++ b/bit/比特配置文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24480" windowHeight="22220"/>
+    <workbookView windowHeight="14640"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="202">
   <si>
     <t>窗口ID</t>
   </si>
@@ -45,6 +45,9 @@
     <t>序号</t>
   </si>
   <si>
+    <t>业务员</t>
+  </si>
+  <si>
     <t>1495e31cb630406bb690ba187f264fe7</t>
   </si>
   <si>
@@ -54,6 +57,9 @@
     <t>墨西哥</t>
   </si>
   <si>
+    <t>张泽文</t>
+  </si>
+  <si>
     <t>9812f185f7ab49d98f3988994d9e8ebf</t>
   </si>
   <si>
@@ -288,7 +294,7 @@
     <t>b1127c7a20bd4952bbc06c41e1b226c5</t>
   </si>
   <si>
-    <t>前程似锦4</t>
+    <t>钱程似锦4</t>
   </si>
   <si>
     <t>00287da1c0964c6889a239c98547b0f5</t>
@@ -1589,8 +1595,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E96"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:F96"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="54.4423076923077" customWidth="1"/>
     <col min="2" max="2" width="15.625" customWidth="1"/>
@@ -1598,7 +1604,7 @@
     <col min="4" max="4" width="31.0288461538462" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:5">
+    <row r="1" ht="14.25" customHeight="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1614,686 +1620,771 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="28.5" customHeight="1" spans="1:5">
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="28.5" customHeight="1" spans="1:6">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E10">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E11">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E12">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E13">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E18">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E20">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E21">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E22">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E23">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E25">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E26">
         <v>29</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E27">
         <v>30</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E28">
         <v>31</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E29">
         <v>32</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E30">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31"/>
+        <v>70</v>
+      </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>34</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32"/>
+        <v>72</v>
+      </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E32">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E33">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E34">
         <v>37</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E35">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E36">
         <v>39</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37"/>
+        <v>82</v>
+      </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E37">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E38">
         <v>41</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39"/>
+        <v>86</v>
+      </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E39">
         <v>42</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E40">
         <v>43</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E41">
         <v>44</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E42">
         <v>45</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E43">
         <v>46</v>
       </c>
-    </row>
-    <row r="44" ht="17.6" spans="1:5">
+      <c r="F43" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" ht="17.6" spans="1:6">
       <c r="A44" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E44">
         <v>47</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E45">
         <v>48</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" t="s">
-        <v>15</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C46"/>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E46">
         <v>49</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E47">
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E48">
         <v>51</v>
@@ -2301,16 +2392,14 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" t="s">
-        <v>15</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C49"/>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E49">
         <v>52</v>
@@ -2318,14 +2407,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
-      </c>
-      <c r="C50"/>
+        <v>107</v>
+      </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E50">
         <v>53</v>
@@ -2333,14 +2421,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51"/>
+        <v>109</v>
+      </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E51">
         <v>55</v>
@@ -2348,13 +2435,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E52">
         <v>56</v>
@@ -2362,13 +2449,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" t="s">
         <v>112</v>
-      </c>
-      <c r="D53" t="s">
-        <v>110</v>
       </c>
       <c r="E53">
         <v>57</v>
@@ -2376,13 +2463,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E54">
         <v>58</v>
@@ -2390,13 +2477,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E55">
         <v>59</v>
@@ -2404,13 +2491,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D56" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E56">
         <v>61</v>
@@ -2418,13 +2505,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E57">
         <v>62</v>
@@ -2432,13 +2519,16 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="C58" t="s">
+        <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E58">
         <v>63</v>
@@ -2446,13 +2536,16 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>125</v>
+        <v>127</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E59">
         <v>64</v>
@@ -2460,13 +2553,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E60">
         <v>65</v>
@@ -2474,13 +2567,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E61">
         <v>66</v>
@@ -2488,14 +2581,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
-      </c>
-      <c r="C62"/>
+        <v>134</v>
+      </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E62">
         <v>67</v>
@@ -2503,14 +2595,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>134</v>
-      </c>
-      <c r="C63"/>
+        <v>136</v>
+      </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E63">
         <v>66</v>
@@ -2518,14 +2609,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
-      </c>
-      <c r="C64"/>
+        <v>138</v>
+      </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E64">
         <v>69</v>
@@ -2533,14 +2623,16 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>138</v>
-      </c>
-      <c r="C65"/>
+        <v>140</v>
+      </c>
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E65">
         <v>70</v>
@@ -2548,14 +2640,16 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>140</v>
-      </c>
-      <c r="C66"/>
+        <v>142</v>
+      </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E66">
         <v>75</v>
@@ -2563,14 +2657,16 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>142</v>
-      </c>
-      <c r="C67"/>
+        <v>144</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E67">
         <v>86</v>
@@ -2578,14 +2674,16 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>144</v>
-      </c>
-      <c r="C68"/>
+        <v>146</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E68">
         <v>89</v>
@@ -2593,14 +2691,16 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
-      </c>
-      <c r="C69"/>
+        <v>148</v>
+      </c>
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E69">
         <v>90</v>
@@ -2608,16 +2708,14 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
-      </c>
-      <c r="C70" t="s">
-        <v>15</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C70"/>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E70">
         <v>94</v>
@@ -2625,16 +2723,14 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B71" t="s">
-        <v>150</v>
-      </c>
-      <c r="C71" t="s">
-        <v>15</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C71"/>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E71">
         <v>95</v>
@@ -2642,16 +2738,14 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B72" t="s">
-        <v>152</v>
-      </c>
-      <c r="C72" t="s">
-        <v>15</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C72"/>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E72">
         <v>96</v>
@@ -2659,16 +2753,14 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B73" t="s">
-        <v>154</v>
-      </c>
-      <c r="C73" t="s">
-        <v>15</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C73"/>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E73">
         <v>97</v>
@@ -2676,16 +2768,14 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B74" t="s">
-        <v>156</v>
-      </c>
-      <c r="C74" t="s">
-        <v>15</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C74"/>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E74">
         <v>98</v>
@@ -2693,13 +2783,13 @@
     </row>
     <row r="75" customFormat="1" spans="1:5">
       <c r="A75" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B75" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D75" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E75">
         <v>101</v>
@@ -2707,13 +2797,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E76">
         <v>102</v>
@@ -2721,13 +2811,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E77">
         <v>103</v>
@@ -2735,13 +2825,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E78">
         <v>104</v>
@@ -2749,13 +2839,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E79">
         <v>105</v>
@@ -2763,13 +2853,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E80">
         <v>106</v>
@@ -2777,13 +2867,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E81">
         <v>107</v>
@@ -2791,13 +2881,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D82" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E82">
         <v>108</v>
@@ -2805,13 +2895,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E83">
         <v>109</v>
@@ -2819,13 +2909,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D84" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E84">
         <v>110</v>
@@ -2833,14 +2923,14 @@
     </row>
     <row r="85" customFormat="1" spans="1:5">
       <c r="A85" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C85"/>
       <c r="D85" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E85">
         <v>111</v>
@@ -2848,13 +2938,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D86" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E86">
         <v>115</v>
@@ -2862,13 +2952,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D87" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E87">
         <v>116</v>
@@ -2876,13 +2966,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D88" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E88">
         <v>117</v>
@@ -2890,13 +2980,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E89">
         <v>118</v>
@@ -2904,13 +2994,16 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B90" t="s">
-        <v>187</v>
+        <v>189</v>
+      </c>
+      <c r="C90" t="s">
+        <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E90">
         <v>119</v>
@@ -2918,16 +3011,16 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B91" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E91">
         <v>123</v>
@@ -2935,10 +3028,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E92">
         <v>127</v>
@@ -2946,10 +3039,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B93" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E93">
         <v>128</v>
@@ -2957,10 +3050,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E94">
         <v>129</v>
@@ -2968,10 +3061,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B95" t="s">
-        <v>197</v>
+        <v>199</v>
+      </c>
+      <c r="C95" t="s">
+        <v>17</v>
       </c>
       <c r="E95">
         <v>130</v>
@@ -2979,10 +3075,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B96" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E96">
         <v>131</v>
@@ -3006,46 +3102,46 @@
   <sheetData>
     <row r="1" ht="17.6" spans="1:4">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="17.6" spans="1:4">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/bit/比特配置文件.xlsx
+++ b/bit/比特配置文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14640"/>
+    <workbookView windowWidth="3264" windowHeight="22320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="176">
   <si>
     <t>窗口ID</t>
   </si>
@@ -87,18 +87,6 @@
     <t>墨西哥，巴西，阿根廷</t>
   </si>
   <si>
-    <t>23abe995037b4efeba2159a0a17df939</t>
-  </si>
-  <si>
-    <t>德德智汇</t>
-  </si>
-  <si>
-    <t>a5cb29d875e84c8580d3f68a0d658533</t>
-  </si>
-  <si>
-    <t>德德智慧</t>
-  </si>
-  <si>
     <t>43e74c662e474a6895fe88874ac88821</t>
   </si>
   <si>
@@ -111,6 +99,9 @@
     <t>四季如春</t>
   </si>
   <si>
+    <t>黄羽飞</t>
+  </si>
+  <si>
     <t>813cdb4042e34e61a78bf16f756df7fc</t>
   </si>
   <si>
@@ -243,6 +234,9 @@
     <t>招财猫</t>
   </si>
   <si>
+    <t>胡瑞泽</t>
+  </si>
+  <si>
     <t>2545d72510084276a752568608eaaf76</t>
   </si>
   <si>
@@ -333,39 +327,21 @@
     <t>发财猪</t>
   </si>
   <si>
-    <t>e042c21cd01c4dfbbdff56c887e44c67</t>
-  </si>
-  <si>
-    <t>赵红</t>
-  </si>
-  <si>
-    <t>钱曼</t>
-  </si>
-  <si>
-    <t>ed544925816a4ec7a7caf47a3ec3ee34</t>
-  </si>
-  <si>
-    <t>雷肖4</t>
-  </si>
-  <si>
     <t>2185db4a008147c688520e54e4e9cfba</t>
   </si>
   <si>
     <t>半托管（腾）</t>
   </si>
   <si>
-    <t>965113a825fb499ba9d45fc685643c48</t>
-  </si>
-  <si>
-    <t>熊心豹胆1</t>
-  </si>
-  <si>
     <t>5678b16fd72d48808ff992154dee8162</t>
   </si>
   <si>
     <t>梁山好汉111</t>
   </si>
   <si>
+    <t>ß</t>
+  </si>
+  <si>
     <t>墨西哥，巴西</t>
   </si>
   <si>
@@ -399,21 +375,6 @@
     <t>流光溢彩</t>
   </si>
   <si>
-    <t>5f319eab69364315a50bc7dbc0fbd4e9</t>
-  </si>
-  <si>
-    <t>宁静致远</t>
-  </si>
-  <si>
-    <t>阿根廷</t>
-  </si>
-  <si>
-    <t>70f84da502fc410482be7d9c994988a0</t>
-  </si>
-  <si>
-    <t>一路长虹</t>
-  </si>
-  <si>
     <t>6ad3c489e6764380a62660578ce986ed</t>
   </si>
   <si>
@@ -429,6 +390,9 @@
     <t>熊心豹胆2</t>
   </si>
   <si>
+    <t>杨雨萌</t>
+  </si>
+  <si>
     <t>cf815071df9146198d240bafc218ff4c</t>
   </si>
   <si>
@@ -447,36 +411,6 @@
     <t>熊心豹胆5</t>
   </si>
   <si>
-    <t>e1430d2f615e456fb197b5ce6b267f3c</t>
-  </si>
-  <si>
-    <t>宁静致远2</t>
-  </si>
-  <si>
-    <t>a1b601a3e3fe4cd893c69007a89feaea</t>
-  </si>
-  <si>
-    <t>宁静致远3</t>
-  </si>
-  <si>
-    <t>30d028302eb644d6b240003e5b923ba6</t>
-  </si>
-  <si>
-    <t>一路长红2</t>
-  </si>
-  <si>
-    <t>b7975c8b198a4b9ca31f5818eebd68cc</t>
-  </si>
-  <si>
-    <t>宁静致远5</t>
-  </si>
-  <si>
-    <t>4c9b4b172c7d404ca71c173c21b6cc4c</t>
-  </si>
-  <si>
-    <t>宁静致远6</t>
-  </si>
-  <si>
     <t>e08adfb6f7384f63846bab2d98c7d022</t>
   </si>
   <si>
@@ -594,12 +528,6 @@
     <t>杨雨萌12</t>
   </si>
   <si>
-    <t>6301596aff0b45ceaccf22ff79ac2fee</t>
-  </si>
-  <si>
-    <t>一路长虹3</t>
-  </si>
-  <si>
     <t>134571ec4f0f4181ac9cdb0d662089c7</t>
   </si>
   <si>
@@ -622,12 +550,6 @@
   </si>
   <si>
     <t>杨雨萌8</t>
-  </si>
-  <si>
-    <t>43c03dd42a594cca87caa850a9d693fd</t>
-  </si>
-  <si>
-    <t>一路长虹5</t>
   </si>
   <si>
     <t>49b850480b2f474fa0bb0ea986800ef8</t>
@@ -1595,7 +1517,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="54.4423076923077" customWidth="1"/>
@@ -1692,6 +1614,9 @@
       <c r="E5">
         <v>4</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
@@ -1707,7 +1632,10 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1717,22 +1645,22 @@
       <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -1741,142 +1669,163 @@
         <v>18</v>
       </c>
       <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="E11">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
         <v>40</v>
       </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>9</v>
@@ -1884,30 +1833,33 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>9</v>
@@ -1915,75 +1867,84 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E20">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>24</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E23">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>9</v>
@@ -1991,16 +1952,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>9</v>
@@ -2008,16 +1969,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>9</v>
@@ -2025,16 +1986,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>9</v>
@@ -2042,16 +2003,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>9</v>
@@ -2059,95 +2020,101 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
       </c>
       <c r="E29">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30">
+        <v>35</v>
+      </c>
+      <c r="F30" t="s">
         <v>68</v>
-      </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30">
-        <v>33</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="E31">
-        <v>34</v>
-      </c>
-      <c r="F31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
       </c>
       <c r="E32">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="E33">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>9</v>
@@ -2155,16 +2122,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
       </c>
       <c r="E35">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>9</v>
@@ -2172,16 +2139,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
       </c>
       <c r="E36">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>9</v>
@@ -2189,16 +2156,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
       </c>
       <c r="E37">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>9</v>
@@ -2206,16 +2173,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
       </c>
       <c r="E38">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>9</v>
@@ -2223,16 +2190,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
       </c>
       <c r="E39">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>9</v>
@@ -2240,16 +2207,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
       </c>
       <c r="E40">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>9</v>
@@ -2257,33 +2224,33 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
       </c>
       <c r="E41">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
-        <v>91</v>
-      </c>
-      <c r="B42" t="s">
-        <v>92</v>
+    <row r="42" ht="17.6" spans="1:6">
+      <c r="A42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
       </c>
       <c r="E42">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>9</v>
@@ -2291,50 +2258,50 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
       </c>
       <c r="E43">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" ht="17.6" spans="1:6">
-      <c r="A44" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>96</v>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" t="s">
+        <v>98</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
       </c>
       <c r="E44">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
       </c>
       <c r="E45">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>9</v>
@@ -2342,746 +2309,619 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46"/>
+        <v>102</v>
+      </c>
+      <c r="C46" t="s">
+        <v>103</v>
+      </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E46">
-        <v>49</v>
-      </c>
-      <c r="F46" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="F46" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>57</v>
+      </c>
+      <c r="F47" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" t="s">
+        <v>104</v>
+      </c>
+      <c r="E48">
+        <v>58</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49">
+        <v>59</v>
+      </c>
+      <c r="F49" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50">
+        <v>61</v>
+      </c>
+      <c r="F50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51">
+        <v>62</v>
+      </c>
+      <c r="F51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" t="s">
+        <v>117</v>
+      </c>
+      <c r="E52">
+        <v>65</v>
+      </c>
+      <c r="F52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53">
+        <v>66</v>
+      </c>
+      <c r="F53" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54">
+        <v>67</v>
+      </c>
+      <c r="F54" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55">
+        <v>66</v>
+      </c>
+      <c r="F55" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56">
+        <v>69</v>
+      </c>
+      <c r="F56" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57">
+        <v>94</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58">
+        <v>95</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>131</v>
+      </c>
+      <c r="B59" t="s">
+        <v>132</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59">
+        <v>96</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" t="s">
+        <v>134</v>
+      </c>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60">
+        <v>97</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61">
+        <v>98</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:6">
+      <c r="A62" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" t="s">
+        <v>138</v>
+      </c>
+      <c r="D62" t="s">
+        <v>117</v>
+      </c>
+      <c r="E62">
+        <v>101</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63">
+        <v>102</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>141</v>
+      </c>
+      <c r="B64" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64">
         <v>103</v>
       </c>
-      <c r="C48" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" t="s">
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" t="s">
+        <v>144</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65">
         <v>104</v>
       </c>
-      <c r="B49" t="s">
+      <c r="F65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" t="s">
+        <v>146</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66">
         <v>105</v>
       </c>
-      <c r="C49"/>
-      <c r="D49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" t="s">
+      <c r="F66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>147</v>
+      </c>
+      <c r="B67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67">
         <v>106</v>
       </c>
-      <c r="B50" t="s">
+      <c r="F67" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68">
         <v>107</v>
       </c>
-      <c r="D50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" t="s">
+      <c r="F68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69">
         <v>108</v>
       </c>
-      <c r="B51" t="s">
+      <c r="F69" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" t="s">
+        <v>153</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70">
         <v>109</v>
       </c>
-      <c r="D51" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" t="s">
+      <c r="F70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+      <c r="B71" t="s">
+        <v>155</v>
+      </c>
+      <c r="D71" t="s">
+        <v>104</v>
+      </c>
+      <c r="E71">
         <v>110</v>
       </c>
-      <c r="B52" t="s">
-        <v>111</v>
-      </c>
-      <c r="D52" t="s">
-        <v>112</v>
-      </c>
-      <c r="E52">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" t="s">
-        <v>113</v>
-      </c>
-      <c r="B53" t="s">
-        <v>114</v>
-      </c>
-      <c r="D53" t="s">
-        <v>112</v>
-      </c>
-      <c r="E53">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" t="s">
-        <v>116</v>
-      </c>
-      <c r="D54" t="s">
-        <v>112</v>
-      </c>
-      <c r="E54">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" t="s">
-        <v>117</v>
-      </c>
-      <c r="B55" t="s">
-        <v>118</v>
-      </c>
-      <c r="D55" t="s">
-        <v>112</v>
-      </c>
-      <c r="E55">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" t="s">
-        <v>119</v>
-      </c>
-      <c r="B56" t="s">
-        <v>120</v>
-      </c>
-      <c r="D56" t="s">
-        <v>112</v>
-      </c>
-      <c r="E56">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" t="s">
-        <v>121</v>
-      </c>
-      <c r="B57" t="s">
-        <v>122</v>
-      </c>
-      <c r="D57" t="s">
-        <v>112</v>
-      </c>
-      <c r="E57">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" t="s">
-        <v>123</v>
-      </c>
-      <c r="B58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C58" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" t="s">
-        <v>125</v>
-      </c>
-      <c r="E58">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" t="s">
-        <v>127</v>
-      </c>
-      <c r="C59" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" t="s">
-        <v>128</v>
-      </c>
-      <c r="B60" t="s">
-        <v>129</v>
-      </c>
-      <c r="D60" t="s">
-        <v>130</v>
-      </c>
-      <c r="E60">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" t="s">
-        <v>131</v>
-      </c>
-      <c r="B61" t="s">
-        <v>132</v>
-      </c>
-      <c r="D61" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" t="s">
-        <v>134</v>
-      </c>
-      <c r="D62" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" t="s">
-        <v>136</v>
-      </c>
-      <c r="D63" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" t="s">
-        <v>137</v>
-      </c>
-      <c r="B64" t="s">
-        <v>138</v>
-      </c>
-      <c r="D64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" t="s">
-        <v>139</v>
-      </c>
-      <c r="B65" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" t="s">
-        <v>141</v>
-      </c>
-      <c r="B66" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" t="s">
-        <v>143</v>
-      </c>
-      <c r="B67" t="s">
-        <v>144</v>
-      </c>
-      <c r="C67" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" t="s">
-        <v>145</v>
-      </c>
-      <c r="B68" t="s">
-        <v>146</v>
-      </c>
-      <c r="C68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" t="s">
-        <v>147</v>
-      </c>
-      <c r="B69" t="s">
-        <v>148</v>
-      </c>
-      <c r="C69" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" t="s">
-        <v>149</v>
-      </c>
-      <c r="B70" t="s">
-        <v>150</v>
-      </c>
-      <c r="C70"/>
-      <c r="D70" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" t="s">
-        <v>151</v>
-      </c>
-      <c r="B71" t="s">
-        <v>152</v>
-      </c>
-      <c r="C71"/>
-      <c r="D71" t="s">
-        <v>18</v>
-      </c>
-      <c r="E71">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:6">
       <c r="A72" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B72" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C72"/>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E72">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>111</v>
+      </c>
+      <c r="F72" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B73" t="s">
-        <v>156</v>
-      </c>
-      <c r="C73"/>
+        <v>159</v>
+      </c>
       <c r="D73" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E73">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>115</v>
+      </c>
+      <c r="F73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
-      </c>
-      <c r="C74"/>
+        <v>161</v>
+      </c>
       <c r="D74" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E74">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" spans="1:5">
+        <v>116</v>
+      </c>
+      <c r="F74" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B75" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D75" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="E75">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>117</v>
+      </c>
+      <c r="F75" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B76" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E76">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>118</v>
+      </c>
+      <c r="F76" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C77"/>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E77">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>123</v>
+      </c>
+      <c r="F77" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E78">
+        <v>127</v>
+      </c>
+      <c r="F78" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>170</v>
+      </c>
+      <c r="B79" t="s">
+        <v>171</v>
+      </c>
+      <c r="D79" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" t="s">
-        <v>167</v>
-      </c>
-      <c r="B79" t="s">
-        <v>168</v>
-      </c>
-      <c r="D79" t="s">
-        <v>18</v>
-      </c>
       <c r="E79">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>128</v>
+      </c>
+      <c r="F79" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D80" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E80">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>129</v>
+      </c>
+      <c r="F80" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B81" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="E81">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" t="s">
-        <v>171</v>
-      </c>
-      <c r="B82" t="s">
-        <v>173</v>
-      </c>
-      <c r="D82" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" t="s">
-        <v>174</v>
-      </c>
-      <c r="B83" t="s">
-        <v>175</v>
-      </c>
-      <c r="D83" t="s">
-        <v>18</v>
-      </c>
-      <c r="E83">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" t="s">
-        <v>176</v>
-      </c>
-      <c r="B84" t="s">
-        <v>177</v>
-      </c>
-      <c r="D84" t="s">
-        <v>112</v>
-      </c>
-      <c r="E84">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="85" customFormat="1" spans="1:5">
-      <c r="A85" t="s">
-        <v>178</v>
-      </c>
-      <c r="B85" t="s">
-        <v>179</v>
-      </c>
-      <c r="C85"/>
-      <c r="D85" t="s">
-        <v>112</v>
-      </c>
-      <c r="E85">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" t="s">
-        <v>180</v>
-      </c>
-      <c r="B86" t="s">
-        <v>181</v>
-      </c>
-      <c r="D86" t="s">
-        <v>112</v>
-      </c>
-      <c r="E86">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" t="s">
-        <v>182</v>
-      </c>
-      <c r="B87" t="s">
-        <v>183</v>
-      </c>
-      <c r="D87" t="s">
-        <v>112</v>
-      </c>
-      <c r="E87">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" t="s">
-        <v>184</v>
-      </c>
-      <c r="B88" t="s">
-        <v>185</v>
-      </c>
-      <c r="D88" t="s">
-        <v>112</v>
-      </c>
-      <c r="E88">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" t="s">
-        <v>186</v>
-      </c>
-      <c r="B89" t="s">
-        <v>187</v>
-      </c>
-      <c r="D89" t="s">
-        <v>112</v>
-      </c>
-      <c r="E89">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" t="s">
-        <v>188</v>
-      </c>
-      <c r="B90" t="s">
-        <v>189</v>
-      </c>
-      <c r="C90" t="s">
-        <v>17</v>
-      </c>
-      <c r="D90" t="s">
-        <v>112</v>
-      </c>
-      <c r="E90">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" t="s">
-        <v>190</v>
-      </c>
-      <c r="B91" t="s">
-        <v>191</v>
-      </c>
-      <c r="C91" t="s">
-        <v>17</v>
-      </c>
-      <c r="D91" t="s">
-        <v>130</v>
-      </c>
-      <c r="E91">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" t="s">
-        <v>192</v>
-      </c>
-      <c r="B92" t="s">
-        <v>193</v>
-      </c>
-      <c r="E92">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" t="s">
-        <v>194</v>
-      </c>
-      <c r="B93" t="s">
-        <v>195</v>
-      </c>
-      <c r="E93">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" t="s">
-        <v>196</v>
-      </c>
-      <c r="B94" t="s">
-        <v>197</v>
-      </c>
-      <c r="E94">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" t="s">
-        <v>198</v>
-      </c>
-      <c r="B95" t="s">
-        <v>199</v>
-      </c>
-      <c r="C95" t="s">
-        <v>17</v>
-      </c>
-      <c r="E95">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" t="s">
-        <v>200</v>
-      </c>
-      <c r="B96" t="s">
-        <v>201</v>
-      </c>
-      <c r="E96">
         <v>131</v>
+      </c>
+      <c r="F81" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3102,10 +2942,10 @@
   <sheetData>
     <row r="1" ht="17.6" spans="1:4">
       <c r="A1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
         <v>18</v>
@@ -3113,10 +2953,10 @@
     </row>
     <row r="2" ht="17.6" spans="1:4">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -3124,10 +2964,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>

--- a/bit/比特配置文件.xlsx
+++ b/bit/比特配置文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="3264" windowHeight="22320"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="243">
   <si>
     <t>窗口ID</t>
   </si>
@@ -48,6 +48,9 @@
     <t>业务员</t>
   </si>
   <si>
+    <t>邮箱</t>
+  </si>
+  <si>
     <t>1495e31cb630406bb690ba187f264fe7</t>
   </si>
   <si>
@@ -60,6 +63,9 @@
     <t>张泽文</t>
   </si>
   <si>
+    <t>vngbjkk@outlook.com</t>
+  </si>
+  <si>
     <t>9812f185f7ab49d98f3988994d9e8ebf</t>
   </si>
   <si>
@@ -69,12 +75,18 @@
     <t>墨西哥，阿根廷</t>
   </si>
   <si>
+    <t>zejianlong@outlook.com</t>
+  </si>
+  <si>
     <t>6af1cc457342417db4e7235d7a062f2f</t>
   </si>
   <si>
     <t>腾</t>
   </si>
   <si>
+    <t>zejianteng@outlook.com</t>
+  </si>
+  <si>
     <t>891d56c43ce0449182bef33695a386ff</t>
   </si>
   <si>
@@ -87,12 +99,18 @@
     <t>墨西哥，巴西，阿根廷</t>
   </si>
   <si>
+    <t>zejianhu@outlook.com</t>
+  </si>
+  <si>
     <t>43e74c662e474a6895fe88874ac88821</t>
   </si>
   <si>
     <t>跃</t>
   </si>
   <si>
+    <t>zejianyue@outlook.com</t>
+  </si>
+  <si>
     <t>22139511815a4bf588fe96d5fdafded6</t>
   </si>
   <si>
@@ -102,6 +120,9 @@
     <t>黄羽飞</t>
   </si>
   <si>
+    <t>huangyufei9991@outlook.com</t>
+  </si>
+  <si>
     <t>813cdb4042e34e61a78bf16f756df7fc</t>
   </si>
   <si>
@@ -114,12 +135,18 @@
     <t>六六大顺</t>
   </si>
   <si>
+    <t>huruize553@outlook.com</t>
+  </si>
+  <si>
     <t>9db3976d84ec44abb07c75af556c5243</t>
   </si>
   <si>
     <t>七星高照</t>
   </si>
   <si>
+    <t>wangyufei553@outlook.com</t>
+  </si>
+  <si>
     <t>5c9af39c13ae47bca3779b2ec55cc481</t>
   </si>
   <si>
@@ -132,6 +159,9 @@
     <t>策马奔腾</t>
   </si>
   <si>
+    <t>huangyufei555@outlook.com</t>
+  </si>
+  <si>
     <t>55d3db6471dc4262aa5dd2de190e2422</t>
   </si>
   <si>
@@ -141,30 +171,45 @@
     <t>巴西，阿根廷</t>
   </si>
   <si>
+    <t>huangyufei111@outlook.com</t>
+  </si>
+  <si>
     <t>c5aac686addf4038aa02cf2d16d1423f</t>
   </si>
   <si>
     <t>钱途无量</t>
   </si>
   <si>
+    <t>huangyufei3333@outlook.com</t>
+  </si>
+  <si>
     <t>d3b94c89e527423aa7f2c5c8dc0a2190</t>
   </si>
   <si>
     <t>鸿运当头</t>
   </si>
   <si>
+    <t>huangyufei580@outlook.com</t>
+  </si>
+  <si>
     <t>b2323ff45855401689ab16ed11d4ed20</t>
   </si>
   <si>
     <t>一跃千里</t>
   </si>
   <si>
+    <t>mercadozeyue@outlook.com</t>
+  </si>
+  <si>
     <t>d49c1865ae404364b05391a79fd6bc65</t>
   </si>
   <si>
     <t>风调雨顺</t>
   </si>
   <si>
+    <t>zejianfeng@outlook.com</t>
+  </si>
+  <si>
     <t>187700d9c3424c0eb6d8a75d92bf3b9c</t>
   </si>
   <si>
@@ -174,60 +219,93 @@
     <t>墨西哥，巴西，智利，阿根廷，乌拉圭</t>
   </si>
   <si>
+    <t>mecadozeyuefti@outlook.com</t>
+  </si>
+  <si>
     <t>3e4c34d0833e4221b262291bddaac899</t>
   </si>
   <si>
     <t>大展宏图</t>
   </si>
   <si>
+    <t>huangyufei521@outlook.com</t>
+  </si>
+  <si>
     <t>764e7e53c57247d7aaa88fb23849f7c9</t>
   </si>
   <si>
     <t>马到成功</t>
   </si>
   <si>
+    <t>hrz159357@outlook.com</t>
+  </si>
+  <si>
     <t>55655ec7c5db43149f5640810197f35c</t>
   </si>
   <si>
     <t>健步如飞</t>
   </si>
   <si>
+    <t>mercadozhangjian@outlook.com</t>
+  </si>
+  <si>
     <t>6190adcc6a3543a8b5fdb7189dfc3802</t>
   </si>
   <si>
     <t>健步如飞1</t>
   </si>
   <si>
+    <t>墨西哥，巴西</t>
+  </si>
+  <si>
+    <t>mercadozhangjian1@outlook.com</t>
+  </si>
+  <si>
     <t>227420bac08049c5a508a2f95510bef4</t>
   </si>
   <si>
     <t>健步如飞2</t>
   </si>
   <si>
+    <t>mercadozhangjian2@outlook.com</t>
+  </si>
+  <si>
     <t>ee50561ad3d242fdb82b42864481a11f</t>
   </si>
   <si>
     <t>健步如飞3</t>
   </si>
   <si>
+    <t>mercadozhangjian3@outlook.com</t>
+  </si>
+  <si>
     <t>3f97a677aba2418081db3f9ca8120fb6</t>
   </si>
   <si>
     <t>飞黄腾达2</t>
   </si>
   <si>
+    <t>zetengmercado2@outlook.com</t>
+  </si>
+  <si>
     <t>8282ffc163ee46c783cc5b4db71f7479</t>
   </si>
   <si>
     <t>飞黄腾达3</t>
   </si>
   <si>
+    <t>zetengmercado3@outlook.com</t>
+  </si>
+  <si>
     <t>33387c91f36241359c0eb0d17be8f974</t>
   </si>
   <si>
     <t>飞黄腾达5</t>
   </si>
   <si>
+    <t>zetengmercado5@outlook.com</t>
+  </si>
+  <si>
     <t>0480d1e8bd84425b9288a8de5fefa1d8</t>
   </si>
   <si>
@@ -237,36 +315,54 @@
     <t>胡瑞泽</t>
   </si>
   <si>
+    <t>wh4700@outlook.com</t>
+  </si>
+  <si>
     <t>2545d72510084276a752568608eaaf76</t>
   </si>
   <si>
     <t>旺财狗</t>
   </si>
   <si>
+    <t>liaoshuo6666@outlook.com</t>
+  </si>
+  <si>
     <t>1449270209804ffda0a7d4e83d22b940</t>
   </si>
   <si>
     <t>杨柳依依1</t>
   </si>
   <si>
+    <t>mercadoyangjiahua1@outlook.com</t>
+  </si>
+  <si>
     <t>2aae34e81b9e40e9860b6658fb7894cc</t>
   </si>
   <si>
     <t>杨柳依依2</t>
   </si>
   <si>
+    <t>mercadoyangjiahua2@outlook.com</t>
+  </si>
+  <si>
     <t>3395db0467064b91988ad8c9b9877412</t>
   </si>
   <si>
     <t>杨柳依依3</t>
   </si>
   <si>
+    <t>mercadoyangjiahua3@outlook.com</t>
+  </si>
+  <si>
     <t>40bcae59448d4745a8622993f1a07cd3</t>
   </si>
   <si>
     <t>杨柳依依4</t>
   </si>
   <si>
+    <t>mercadoyangjiahua4@outlook.com</t>
+  </si>
+  <si>
     <t>315b0b0575884e7181cefaa8a6301f96</t>
   </si>
   <si>
@@ -279,6 +375,9 @@
     <t>钱程似锦2</t>
   </si>
   <si>
+    <t>mecadoqianjun2@outlook.com</t>
+  </si>
+  <si>
     <t>987270a6587b46eeaeac11e9b928e88d</t>
   </si>
   <si>
@@ -291,42 +390,66 @@
     <t>钱程似锦4</t>
   </si>
   <si>
+    <t>mecadoqianjun4@outlook.com</t>
+  </si>
+  <si>
     <t>00287da1c0964c6889a239c98547b0f5</t>
   </si>
   <si>
     <t>钱程似锦5</t>
   </si>
   <si>
+    <t>mecadoqianjun5@outlook.com</t>
+  </si>
+  <si>
     <t>df2d33b20d0b4d72949fc490f7ff075a</t>
   </si>
   <si>
     <t>龙争虎斗</t>
   </si>
   <si>
+    <t>巴西</t>
+  </si>
+  <si>
+    <t>mercadozelong@outlook.com</t>
+  </si>
+  <si>
     <t>b2f7baeb363346af8d81dd20dd945ef4</t>
   </si>
   <si>
     <t>龙马精神</t>
   </si>
   <si>
+    <t>zelongmercado1@outlook.com</t>
+  </si>
+  <si>
     <t>1f22b75033a84d64bff59c3a41ea6047</t>
   </si>
   <si>
     <t>龙吟虎啸</t>
   </si>
   <si>
+    <t>zelongmercado2@outlook.com</t>
+  </si>
+  <si>
     <t>38fcac77fbf641ed8b6cbc1c2aedc5b2</t>
   </si>
   <si>
     <t>龙凤呈祥</t>
   </si>
   <si>
+    <t>zelongmercado3@outlook.com</t>
+  </si>
+  <si>
     <t>a6de8a3a7776481faedf942cd1928a3d</t>
   </si>
   <si>
     <t>发财猪</t>
   </si>
   <si>
+    <t>liaoshuo8888@outlook.com</t>
+  </si>
+  <si>
     <t>2185db4a008147c688520e54e4e9cfba</t>
   </si>
   <si>
@@ -339,10 +462,7 @@
     <t>梁山好汉111</t>
   </si>
   <si>
-    <t>ß</t>
-  </si>
-  <si>
-    <t>墨西哥，巴西</t>
+    <t>mingmingerr@outlook.com</t>
   </si>
   <si>
     <t>dae8490852304cf3a08d8a68a137dae1</t>
@@ -351,30 +471,45 @@
     <t>梁山好汉222</t>
   </si>
   <si>
+    <t>xinhuilaicai666@outlook.com</t>
+  </si>
+  <si>
     <t>762be65d5a9f49419c5a2c5ff719377c</t>
   </si>
   <si>
     <t>梁山好汉333</t>
   </si>
   <si>
+    <t>xinhuilaicai888@outlook.com</t>
+  </si>
+  <si>
     <t>f0166632424340dc801961780e7de4c9</t>
   </si>
   <si>
     <t>梁山好汉666</t>
   </si>
   <si>
+    <t>mingmingliang111@outlook.com</t>
+  </si>
+  <si>
     <t>6ae1546ec1a54940b1408636e2f57bc9</t>
   </si>
   <si>
     <t>光彩夺目</t>
   </si>
   <si>
+    <t>tingfei333@outlook.com</t>
+  </si>
+  <si>
     <t>56069948a074419b8c70f15cc06e208c</t>
   </si>
   <si>
     <t>流光溢彩</t>
   </si>
   <si>
+    <t>kangzhuotingfei111@outlook.com</t>
+  </si>
+  <si>
     <t>6ad3c489e6764380a62660578ce986ed</t>
   </si>
   <si>
@@ -384,6 +519,9 @@
     <t>墨西哥，巴西，智利，阿根廷，乌拉圭，哥伦比亚</t>
   </si>
   <si>
+    <t>mercadozehufti@outlook.com</t>
+  </si>
+  <si>
     <t>b9d071b27bb14d228c0fcf930f532f78</t>
   </si>
   <si>
@@ -417,42 +555,63 @@
     <t>张健1</t>
   </si>
   <si>
+    <t>mercadozhangjianzj@outlook.com</t>
+  </si>
+  <si>
     <t>8e3a288675494673b1f60c7bebaa0948</t>
   </si>
   <si>
     <t>张健2</t>
   </si>
   <si>
+    <t>mercadozhangjianzj2@outlook.com</t>
+  </si>
+  <si>
     <t>0e49e9e24c3445c4b2819c44958b7066</t>
   </si>
   <si>
     <t>张健3</t>
   </si>
   <si>
+    <t>mercadozhangjianzj3@outlook.com</t>
+  </si>
+  <si>
     <t>fba66b9f4e9444648f8d8c2c0bc6a2ab</t>
   </si>
   <si>
     <t>张健5</t>
   </si>
   <si>
+    <t>mercadozhangjianzj5@outlook.com</t>
+  </si>
+  <si>
     <t>3387784b60af4856b32ae823c89ce015</t>
   </si>
   <si>
     <t>张健6</t>
   </si>
   <si>
+    <t>mercadozhangjianzj6@outlook.com</t>
+  </si>
+  <si>
     <t>b15c1542fb154a68b6ffbee7b868c33d</t>
   </si>
   <si>
     <t>健步如飞（fti）</t>
   </si>
   <si>
+    <t>mercadozhangjianfti@outlook.com</t>
+  </si>
+  <si>
     <t>ab4d7d7e9b78450181f485d2253f6d37</t>
   </si>
   <si>
     <t>高风亮节</t>
   </si>
   <si>
+    <t>yugaohan333@outlook.com</t>
+  </si>
+  <si>
     <t>19ba260e1440411196fdedfd4242fb51</t>
   </si>
   <si>
@@ -465,51 +624,78 @@
     <t>高人一等</t>
   </si>
   <si>
+    <t>yugaohan111@outlook.com</t>
+  </si>
+  <si>
     <t>5b090a4484324c86a4d747574ddd0456</t>
   </si>
   <si>
     <t>金光闪闪</t>
   </si>
   <si>
+    <t>jinxiyuan555@outlook.com</t>
+  </si>
+  <si>
     <t>4e712461dab04cdaa46f5400a4e8d3c6</t>
   </si>
   <si>
     <t>功成名就</t>
   </si>
   <si>
+    <t>xinhuilaicai111@outlook.com</t>
+  </si>
+  <si>
     <t>76e9492d6e5d4d3c9a564ed5efeb7b74</t>
   </si>
   <si>
     <t>顺财羊</t>
   </si>
   <si>
+    <t>jinxiyuan222@outlook.com</t>
+  </si>
+  <si>
     <t>杨雨萌2</t>
   </si>
   <si>
+    <t>yangyumengmercado2@outlook.com</t>
+  </si>
+  <si>
     <t>b4a18a93a06f41a58fee027c3a9921c3</t>
   </si>
   <si>
     <t>来财马</t>
   </si>
   <si>
+    <t>jinxiyuan111@outlook.com</t>
+  </si>
+  <si>
     <t>b2e795192e7144678fc01f9b50e383f1</t>
   </si>
   <si>
     <t>聚财鼠</t>
   </si>
   <si>
+    <t>jinxiyuan333@outlook.com</t>
+  </si>
+  <si>
     <t>cdc4b2cf5d5843eea6b138f2a1c438c1</t>
   </si>
   <si>
     <t>杨雨萌5</t>
   </si>
   <si>
+    <t>mercadoyangyumeng5@outlook.com</t>
+  </si>
+  <si>
     <t>5c4a6dfd6c8a4c22b260d2f7f2266d96</t>
   </si>
   <si>
     <t>杨雨萌3</t>
   </si>
   <si>
+    <t>mercadoyangyumeng3@outlook.com</t>
+  </si>
+  <si>
     <t>66a4f57563c142ed9297b79a5e0eed7f</t>
   </si>
   <si>
@@ -528,28 +714,43 @@
     <t>杨雨萌12</t>
   </si>
   <si>
+    <t>mercadoyangyumeng11@outlook.com</t>
+  </si>
+  <si>
     <t>134571ec4f0f4181ac9cdb0d662089c7</t>
   </si>
   <si>
     <t>顺风顺水(fti)</t>
   </si>
   <si>
+    <t>mercadozhangzewenfti@outlook.com</t>
+  </si>
+  <si>
     <t>e43120bd287e460281d97e91dc55009c</t>
   </si>
   <si>
     <t>杨雨萌6</t>
   </si>
   <si>
+    <t>mercadoyangyumeng6@outlook.com</t>
+  </si>
+  <si>
     <t>363cdd70c2964fb29953b1f5d6fbab52</t>
   </si>
   <si>
     <t>杨雨萌7</t>
   </si>
   <si>
+    <t>mercadoyangyumeng7@outlook.com</t>
+  </si>
+  <si>
     <t>447e934e9e0449959d29d07b61e3b154</t>
   </si>
   <si>
     <t>杨雨萌8</t>
+  </si>
+  <si>
+    <t>mercadoyangyumeng8@outlook.com</t>
   </si>
   <si>
     <t>49b850480b2f474fa0bb0ea986800ef8</t>
@@ -1190,7 +1391,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1204,6 +1405,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1517,16 +1727,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:G80"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="54.4423076923077" customWidth="1"/>
+    <col min="1" max="1" width="54.4416666666667" customWidth="1"/>
     <col min="2" max="2" width="15.625" customWidth="1"/>
     <col min="3" max="3" width="25.75" customWidth="1"/>
-    <col min="4" max="4" width="31.0288461538462" customWidth="1"/>
+    <col min="4" max="4" width="31.025" customWidth="1"/>
+    <col min="7" max="7" width="29.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:6">
+    <row r="1" ht="14.25" customHeight="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1545,1389 +1756,1658 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="28.5" customHeight="1" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="28.5" customHeight="1" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>29</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E8">
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E9">
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>29</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E10">
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>29</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E11">
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>29</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E13">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>29</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E14">
         <v>20</v>
       </c>
       <c r="F14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16">
+        <v>22</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15">
-        <v>20</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="F17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18">
+        <v>24</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20">
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21">
+        <v>27</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22">
+        <v>28</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24">
+        <v>30</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25">
+        <v>31</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26">
+        <v>32</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27">
+        <v>33</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28">
+        <v>34</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29">
+        <v>35</v>
+      </c>
+      <c r="F29" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30">
+        <v>36</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31">
+        <v>37</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32">
+        <v>38</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33">
         <v>39</v>
       </c>
-      <c r="B16" t="s">
+      <c r="F33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34">
         <v>40</v>
       </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16">
+      <c r="F34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="5"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35">
+        <v>41</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" t="s">
         <v>21</v>
       </c>
-      <c r="F16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="D36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36">
         <v>42</v>
       </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17">
-        <v>22</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="F36" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37">
         <v>43</v>
       </c>
-      <c r="B18" t="s">
+      <c r="F37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38">
         <v>44</v>
       </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18">
-        <v>23</v>
-      </c>
-      <c r="F18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39">
         <v>45</v>
       </c>
-      <c r="B19" t="s">
+      <c r="F39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40">
         <v>46</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" spans="1:7">
+      <c r="A41" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41">
         <v>47</v>
       </c>
-      <c r="E19">
-        <v>24</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+      <c r="F41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42">
         <v>48</v>
       </c>
-      <c r="B20" t="s">
+      <c r="F42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43">
         <v>49</v>
       </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20">
-        <v>25</v>
-      </c>
-      <c r="F20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21">
-        <v>26</v>
-      </c>
-      <c r="F21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="F43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G43" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44">
         <v>53</v>
       </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22">
-        <v>27</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+      <c r="F44" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45"/>
+      <c r="D45" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45">
         <v>56</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F45" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46">
         <v>57</v>
       </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24">
+      <c r="F46" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+      <c r="G46" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47">
         <v>58</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F47" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" t="s">
+        <v>152</v>
+      </c>
+      <c r="D48" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48">
         <v>59</v>
       </c>
-      <c r="D25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25">
-        <v>30</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="F48" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49">
         <v>61</v>
       </c>
-      <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26">
-        <v>31</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="F49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>157</v>
+      </c>
+      <c r="B50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D50" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50">
         <v>62</v>
       </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27">
-        <v>32</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="F50" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" t="s">
+        <v>161</v>
+      </c>
+      <c r="D51" t="s">
+        <v>162</v>
+      </c>
+      <c r="E51">
         <v>65</v>
       </c>
-      <c r="D28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28">
-        <v>33</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" t="s">
+        <v>165</v>
+      </c>
+      <c r="C52" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52">
         <v>66</v>
       </c>
-      <c r="B29" t="s">
+      <c r="F52" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53">
         <v>67</v>
       </c>
-      <c r="D29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29">
-        <v>34</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="F53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54">
+        <v>66</v>
+      </c>
+      <c r="F54" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>171</v>
+      </c>
+      <c r="B55" t="s">
+        <v>172</v>
+      </c>
+      <c r="C55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55">
         <v>69</v>
       </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30">
-        <v>35</v>
-      </c>
-      <c r="F30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31">
-        <v>36</v>
-      </c>
-      <c r="F31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32">
-        <v>37</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
+      <c r="F55" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56">
+        <v>94</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>176</v>
+      </c>
+      <c r="B57" t="s">
+        <v>177</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57">
+        <v>95</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>179</v>
+      </c>
+      <c r="B58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58">
+        <v>96</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" t="s">
+        <v>183</v>
+      </c>
+      <c r="D59" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59">
+        <v>97</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" t="s">
+        <v>186</v>
+      </c>
+      <c r="C60" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60">
+        <v>98</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:7">
+      <c r="A61" t="s">
+        <v>188</v>
+      </c>
+      <c r="B61" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" t="s">
+        <v>162</v>
+      </c>
+      <c r="E61">
+        <v>101</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>191</v>
+      </c>
+      <c r="B62" t="s">
+        <v>192</v>
+      </c>
+      <c r="D62" t="s">
+        <v>46</v>
+      </c>
+      <c r="E62">
+        <v>102</v>
+      </c>
+      <c r="F62" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>194</v>
+      </c>
+      <c r="B63" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63">
+        <v>103</v>
+      </c>
+      <c r="F63" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>196</v>
+      </c>
+      <c r="B64" t="s">
+        <v>197</v>
+      </c>
+      <c r="D64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64">
+        <v>104</v>
+      </c>
+      <c r="F64" t="s">
+        <v>29</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>199</v>
+      </c>
+      <c r="B65" t="s">
+        <v>200</v>
+      </c>
+      <c r="D65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65">
+        <v>105</v>
+      </c>
+      <c r="F65" t="s">
+        <v>29</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>202</v>
+      </c>
+      <c r="B66" t="s">
+        <v>203</v>
+      </c>
+      <c r="D66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66">
+        <v>106</v>
+      </c>
+      <c r="F66" t="s">
+        <v>29</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>205</v>
+      </c>
+      <c r="B67" t="s">
+        <v>206</v>
+      </c>
+      <c r="D67" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67">
+        <v>107</v>
+      </c>
+      <c r="F67" t="s">
+        <v>94</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>205</v>
+      </c>
+      <c r="B68" t="s">
+        <v>208</v>
+      </c>
+      <c r="D68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68">
+        <v>108</v>
+      </c>
+      <c r="F68" t="s">
+        <v>166</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>210</v>
+      </c>
+      <c r="B69" t="s">
+        <v>211</v>
+      </c>
+      <c r="D69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69">
+        <v>109</v>
+      </c>
+      <c r="F69" t="s">
+        <v>94</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>213</v>
+      </c>
+      <c r="B70" t="s">
+        <v>214</v>
+      </c>
+      <c r="D70" t="s">
         <v>75</v>
       </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33">
-        <v>38</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34">
-        <v>39</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35">
-        <v>40</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36">
-        <v>41</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37">
-        <v>42</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38">
-        <v>43</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39">
-        <v>44</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40">
-        <v>45</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41">
-        <v>46</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" ht="17.6" spans="1:6">
-      <c r="A42" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" s="1" t="s">
+      <c r="E70">
+        <v>110</v>
+      </c>
+      <c r="F70" t="s">
         <v>94</v>
       </c>
-      <c r="D42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42">
-        <v>47</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" t="s">
-        <v>96</v>
-      </c>
-      <c r="D43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43">
-        <v>48</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
-        <v>97</v>
-      </c>
-      <c r="B44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44">
-        <v>49</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45">
-        <v>53</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
-        <v>101</v>
-      </c>
-      <c r="B46" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46">
-        <v>56</v>
-      </c>
-      <c r="F46" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
-        <v>105</v>
-      </c>
-      <c r="B47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>104</v>
-      </c>
-      <c r="E47">
-        <v>57</v>
-      </c>
-      <c r="F47" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
-        <v>107</v>
-      </c>
-      <c r="B48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D48" t="s">
-        <v>104</v>
-      </c>
-      <c r="E48">
-        <v>58</v>
-      </c>
-      <c r="F48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
-        <v>109</v>
-      </c>
-      <c r="B49" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" t="s">
-        <v>104</v>
-      </c>
-      <c r="E49">
-        <v>59</v>
-      </c>
-      <c r="F49" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
+      <c r="G70" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:7">
+      <c r="A71" t="s">
+        <v>216</v>
+      </c>
+      <c r="B71" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71"/>
+      <c r="D71" t="s">
+        <v>75</v>
+      </c>
+      <c r="E71">
         <v>111</v>
       </c>
-      <c r="B50" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" t="s">
-        <v>104</v>
-      </c>
-      <c r="E50">
-        <v>61</v>
-      </c>
-      <c r="F50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
-        <v>113</v>
-      </c>
-      <c r="B51" t="s">
-        <v>114</v>
-      </c>
-      <c r="D51" t="s">
-        <v>104</v>
-      </c>
-      <c r="E51">
-        <v>62</v>
-      </c>
-      <c r="F51" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
+      <c r="F71" t="s">
+        <v>166</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>219</v>
+      </c>
+      <c r="B72" t="s">
+        <v>220</v>
+      </c>
+      <c r="D72" t="s">
+        <v>75</v>
+      </c>
+      <c r="E72">
         <v>115</v>
       </c>
-      <c r="B52" t="s">
+      <c r="F72" t="s">
+        <v>166</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>222</v>
+      </c>
+      <c r="B73" t="s">
+        <v>223</v>
+      </c>
+      <c r="D73" t="s">
+        <v>75</v>
+      </c>
+      <c r="E73">
         <v>116</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F73" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>224</v>
+      </c>
+      <c r="B74" t="s">
+        <v>225</v>
+      </c>
+      <c r="D74" t="s">
+        <v>75</v>
+      </c>
+      <c r="E74">
         <v>117</v>
       </c>
-      <c r="E52">
-        <v>65</v>
-      </c>
-      <c r="F52" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
+      <c r="F74" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>226</v>
+      </c>
+      <c r="B75" t="s">
+        <v>227</v>
+      </c>
+      <c r="D75" t="s">
+        <v>75</v>
+      </c>
+      <c r="E75">
         <v>118</v>
       </c>
-      <c r="B53" t="s">
-        <v>119</v>
-      </c>
-      <c r="D53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53">
-        <v>66</v>
-      </c>
-      <c r="F53" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" t="s">
-        <v>122</v>
-      </c>
-      <c r="D54" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54">
-        <v>67</v>
-      </c>
-      <c r="F54" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
+      <c r="F75" t="s">
+        <v>166</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>229</v>
+      </c>
+      <c r="B76" t="s">
+        <v>230</v>
+      </c>
+      <c r="D76" t="s">
+        <v>162</v>
+      </c>
+      <c r="E76">
         <v>123</v>
       </c>
-      <c r="B55" t="s">
-        <v>124</v>
-      </c>
-      <c r="D55" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55">
-        <v>66</v>
-      </c>
-      <c r="F55" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56">
-        <v>69</v>
-      </c>
-      <c r="F56" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
+      <c r="F76" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>232</v>
+      </c>
+      <c r="B77" t="s">
+        <v>233</v>
+      </c>
+      <c r="D77" t="s">
+        <v>75</v>
+      </c>
+      <c r="E77">
         <v>127</v>
       </c>
-      <c r="B57" t="s">
+      <c r="F77" t="s">
+        <v>166</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>235</v>
+      </c>
+      <c r="B78" t="s">
+        <v>236</v>
+      </c>
+      <c r="D78" t="s">
+        <v>75</v>
+      </c>
+      <c r="E78">
         <v>128</v>
       </c>
-      <c r="D57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57">
-        <v>94</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
+      <c r="F78" t="s">
+        <v>166</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>238</v>
+      </c>
+      <c r="B79" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" t="s">
+        <v>75</v>
+      </c>
+      <c r="E79">
         <v>129</v>
       </c>
-      <c r="B58" t="s">
-        <v>130</v>
-      </c>
-      <c r="D58" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58">
-        <v>95</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
+      <c r="F79" t="s">
+        <v>166</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>241</v>
+      </c>
+      <c r="B80" t="s">
+        <v>242</v>
+      </c>
+      <c r="D80" t="s">
+        <v>75</v>
+      </c>
+      <c r="E80">
         <v>131</v>
       </c>
-      <c r="B59" t="s">
-        <v>132</v>
-      </c>
-      <c r="D59" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59">
-        <v>96</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
-        <v>133</v>
-      </c>
-      <c r="B60" t="s">
-        <v>134</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60">
-        <v>97</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
-        <v>135</v>
-      </c>
-      <c r="B61" t="s">
-        <v>136</v>
-      </c>
-      <c r="D61" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61">
-        <v>98</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" spans="1:6">
-      <c r="A62" t="s">
-        <v>137</v>
-      </c>
-      <c r="B62" t="s">
-        <v>138</v>
-      </c>
-      <c r="D62" t="s">
-        <v>117</v>
-      </c>
-      <c r="E62">
-        <v>101</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
-        <v>139</v>
-      </c>
-      <c r="B63" t="s">
-        <v>140</v>
-      </c>
-      <c r="D63" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63">
-        <v>102</v>
-      </c>
-      <c r="F63" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" t="s">
-        <v>141</v>
-      </c>
-      <c r="B64" t="s">
-        <v>142</v>
-      </c>
-      <c r="D64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64">
-        <v>103</v>
-      </c>
-      <c r="F64" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
-        <v>143</v>
-      </c>
-      <c r="B65" t="s">
-        <v>144</v>
-      </c>
-      <c r="D65" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65">
-        <v>104</v>
-      </c>
-      <c r="F65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
-        <v>145</v>
-      </c>
-      <c r="B66" t="s">
-        <v>146</v>
-      </c>
-      <c r="D66" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66">
-        <v>105</v>
-      </c>
-      <c r="F66" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
-        <v>147</v>
-      </c>
-      <c r="B67" t="s">
-        <v>148</v>
-      </c>
-      <c r="D67" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67">
-        <v>106</v>
-      </c>
-      <c r="F67" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" t="s">
-        <v>150</v>
-      </c>
-      <c r="D68" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68">
-        <v>107</v>
-      </c>
-      <c r="F68" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" t="s">
-        <v>151</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69">
-        <v>108</v>
-      </c>
-      <c r="F69" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
-        <v>152</v>
-      </c>
-      <c r="B70" t="s">
-        <v>153</v>
-      </c>
-      <c r="D70" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70">
-        <v>109</v>
-      </c>
-      <c r="F70" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
-        <v>154</v>
-      </c>
-      <c r="B71" t="s">
-        <v>155</v>
-      </c>
-      <c r="D71" t="s">
-        <v>104</v>
-      </c>
-      <c r="E71">
-        <v>110</v>
-      </c>
-      <c r="F71" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="72" customFormat="1" spans="1:6">
-      <c r="A72" t="s">
-        <v>156</v>
-      </c>
-      <c r="B72" t="s">
-        <v>157</v>
-      </c>
-      <c r="C72"/>
-      <c r="D72" t="s">
-        <v>104</v>
-      </c>
-      <c r="E72">
-        <v>111</v>
-      </c>
-      <c r="F72" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
-        <v>158</v>
-      </c>
-      <c r="B73" t="s">
-        <v>159</v>
-      </c>
-      <c r="D73" t="s">
-        <v>104</v>
-      </c>
-      <c r="E73">
-        <v>115</v>
-      </c>
-      <c r="F73" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
-        <v>160</v>
-      </c>
-      <c r="B74" t="s">
-        <v>161</v>
-      </c>
-      <c r="D74" t="s">
-        <v>104</v>
-      </c>
-      <c r="E74">
-        <v>116</v>
-      </c>
-      <c r="F74" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
-        <v>162</v>
-      </c>
-      <c r="B75" t="s">
-        <v>163</v>
-      </c>
-      <c r="D75" t="s">
-        <v>104</v>
-      </c>
-      <c r="E75">
-        <v>117</v>
-      </c>
-      <c r="F75" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
-        <v>164</v>
-      </c>
-      <c r="B76" t="s">
-        <v>165</v>
-      </c>
-      <c r="D76" t="s">
-        <v>104</v>
-      </c>
-      <c r="E76">
-        <v>118</v>
-      </c>
-      <c r="F76" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
+      <c r="F80" t="s">
         <v>166</v>
-      </c>
-      <c r="B77" t="s">
-        <v>167</v>
-      </c>
-      <c r="C77"/>
-      <c r="D77" t="s">
-        <v>117</v>
-      </c>
-      <c r="E77">
-        <v>123</v>
-      </c>
-      <c r="F77" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
-        <v>168</v>
-      </c>
-      <c r="B78" t="s">
-        <v>169</v>
-      </c>
-      <c r="D78" t="s">
-        <v>104</v>
-      </c>
-      <c r="E78">
-        <v>127</v>
-      </c>
-      <c r="F78" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
-        <v>170</v>
-      </c>
-      <c r="B79" t="s">
-        <v>171</v>
-      </c>
-      <c r="D79" t="s">
-        <v>104</v>
-      </c>
-      <c r="E79">
-        <v>128</v>
-      </c>
-      <c r="F79" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
-        <v>172</v>
-      </c>
-      <c r="B80" t="s">
-        <v>173</v>
-      </c>
-      <c r="D80" t="s">
-        <v>104</v>
-      </c>
-      <c r="E80">
-        <v>129</v>
-      </c>
-      <c r="F80" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" t="s">
-        <v>174</v>
-      </c>
-      <c r="B81" t="s">
-        <v>175</v>
-      </c>
-      <c r="D81" t="s">
-        <v>104</v>
-      </c>
-      <c r="E81">
-        <v>131</v>
-      </c>
-      <c r="F81" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A2:E44">
     <sortCondition ref="E2"/>
   </sortState>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="vngbjkk@outlook.com"/>
+    <hyperlink ref="G3" r:id="rId2" display="zejianlong@outlook.com"/>
+    <hyperlink ref="G4" r:id="rId3" display="zejianteng@outlook.com" tooltip="mailto:zejianteng@outlook.com"/>
+    <hyperlink ref="G5" r:id="rId4" display="zejianhu@outlook.com"/>
+    <hyperlink ref="G6" r:id="rId5" display="zejianyue@outlook.com"/>
+    <hyperlink ref="G7" r:id="rId6" display="huangyufei9991@outlook.com"/>
+    <hyperlink ref="G9" r:id="rId7" display="huruize553@outlook.com"/>
+    <hyperlink ref="G10" r:id="rId8" display="wangyufei553@outlook.com"/>
+    <hyperlink ref="G12" r:id="rId9" display="huangyufei555@outlook.com"/>
+    <hyperlink ref="G13" r:id="rId10" display="huangyufei111@outlook.com"/>
+    <hyperlink ref="G14" r:id="rId11" display="huangyufei3333@outlook.com"/>
+    <hyperlink ref="G17" r:id="rId12" display="zejianfeng@outlook.com"/>
+    <hyperlink ref="G18" r:id="rId13" display="mecadozeyuefti@outlook.com"/>
+    <hyperlink ref="G19" r:id="rId14" display="huangyufei521@outlook.com"/>
+    <hyperlink ref="G21" r:id="rId15" display="mercadozhangjian@outlook.com"/>
+    <hyperlink ref="G22" r:id="rId16" display="mercadozhangjian1@outlook.com"/>
+    <hyperlink ref="G23" r:id="rId17" display="mercadozhangjian2@outlook.com"/>
+    <hyperlink ref="G24" r:id="rId18" display="mercadozhangjian3@outlook.com"/>
+    <hyperlink ref="G25" r:id="rId19" display="zetengmercado2@outlook.com"/>
+    <hyperlink ref="G26" r:id="rId20" display="zetengmercado3@outlook.com"/>
+    <hyperlink ref="G27" r:id="rId21" display="zetengmercado5@outlook.com"/>
+    <hyperlink ref="G28" r:id="rId22" display="wh4700@outlook.com"/>
+    <hyperlink ref="G29" r:id="rId23" display="liaoshuo6666@outlook.com"/>
+    <hyperlink ref="G30" r:id="rId24" display="mercadoyangjiahua1@outlook.com"/>
+    <hyperlink ref="G31" r:id="rId25" display="mercadoyangjiahua2@outlook.com"/>
+    <hyperlink ref="G32" r:id="rId26" display="mercadoyangjiahua3@outlook.com"/>
+    <hyperlink ref="G33" r:id="rId27" display="mercadoyangjiahua4@outlook.com"/>
+    <hyperlink ref="G35" r:id="rId28" display="mecadoqianjun2@outlook.com"/>
+    <hyperlink ref="G37" r:id="rId29" display="mecadoqianjun4@outlook.com"/>
+    <hyperlink ref="G38" r:id="rId30" display="mecadoqianjun5@outlook.com"/>
+    <hyperlink ref="G40" r:id="rId31" display="zelongmercado1@outlook.com"/>
+    <hyperlink ref="G39" r:id="rId32" display="mercadozelong@outlook.com"/>
+    <hyperlink ref="G41" r:id="rId33" display="zelongmercado2@outlook.com"/>
+    <hyperlink ref="G42" r:id="rId34" display="zelongmercado3@outlook.com"/>
+    <hyperlink ref="G45" r:id="rId35" display="mingmingerr@outlook.com"/>
+    <hyperlink ref="G47" r:id="rId36" display="xinhuilaicai888@outlook.com"/>
+    <hyperlink ref="G48" r:id="rId37" display="mingmingliang111@outlook.com"/>
+    <hyperlink ref="G49" r:id="rId38" display="tingfei333@outlook.com"/>
+    <hyperlink ref="G50" r:id="rId39" display="kangzhuotingfei111@outlook.com"/>
+    <hyperlink ref="G51" r:id="rId40" display="mercadozehufti@outlook.com"/>
+    <hyperlink ref="G56" r:id="rId41" display="mercadozhangjianzj@outlook.com"/>
+    <hyperlink ref="G57" r:id="rId42" display="mercadozhangjianzj2@outlook.com" tooltip="mailto:mercadozhangjianzj2@outlook.com"/>
+    <hyperlink ref="G58" r:id="rId43" display="mercadozhangjianzj3@outlook.com"/>
+    <hyperlink ref="G59" r:id="rId44" display="mercadozhangjianzj5@outlook.com"/>
+    <hyperlink ref="G60" r:id="rId45" display="mercadozhangjianzj6@outlook.com"/>
+    <hyperlink ref="G61" r:id="rId46" display="mercadozhangjianfti@outlook.com"/>
+    <hyperlink ref="G62" r:id="rId47" display="yugaohan333@outlook.com"/>
+    <hyperlink ref="G64" r:id="rId48" display="yugaohan111@outlook.com"/>
+    <hyperlink ref="G65" r:id="rId49" display="jinxiyuan555@outlook.com"/>
+    <hyperlink ref="G66" r:id="rId50" display="xinhuilaicai111@outlook.com"/>
+    <hyperlink ref="G67" r:id="rId51" display="jinxiyuan222@outlook.com"/>
+    <hyperlink ref="G68" r:id="rId52" display="yangyumengmercado2@outlook.com"/>
+    <hyperlink ref="G69" r:id="rId53" display="jinxiyuan111@outlook.com"/>
+    <hyperlink ref="G70" r:id="rId54" display="jinxiyuan333@outlook.com"/>
+    <hyperlink ref="G71" r:id="rId55" display="mercadoyangyumeng5@outlook.com"/>
+    <hyperlink ref="G72" r:id="rId56" display="mercadoyangyumeng3@outlook.com"/>
+    <hyperlink ref="G75" r:id="rId57" display="mercadoyangyumeng11@outlook.com"/>
+    <hyperlink ref="G76" r:id="rId58" display="mercadozhangzewenfti@outlook.com"/>
+    <hyperlink ref="G77" r:id="rId59" display="mercadoyangyumeng6@outlook.com"/>
+    <hyperlink ref="G78" r:id="rId60" display="mercadoyangyumeng7@outlook.com"/>
+    <hyperlink ref="G79" r:id="rId61" display="mercadoyangyumeng8@outlook.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2938,50 +3418,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.61538461538461" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.61666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" ht="17.6" spans="1:4">
+    <row r="1" ht="14.25" spans="1:4">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" ht="17.6" spans="1:4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:4">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
